--- a/wwwroot/template/FileSelectionQuote.xlsx
+++ b/wwwroot/template/FileSelectionQuote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A3719B-55C1-49B2-B28F-3276170E55E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D8236DB-27E6-4047-8F0C-ABC33FD23676}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D8236DB-27E6-4047-8F0C-ABC33FD23676}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -663,24 +663,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -694,6 +676,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1055,224 +1055,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="11" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-      <c r="AI1" s="11"/>
-      <c r="AJ1" s="11"/>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="11"/>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
-      <c r="AO1" s="11"/>
-      <c r="AP1" s="11"/>
-      <c r="AQ1" s="11"/>
-      <c r="AR1" s="11"/>
-      <c r="AS1" s="11"/>
-      <c r="AT1" s="11"/>
-      <c r="AU1" s="11"/>
-      <c r="AV1" s="11"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="17"/>
+      <c r="AS1" s="17"/>
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17"/>
+      <c r="AV1" s="17"/>
       <c r="AW1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AX1" s="9" t="s">
+      <c r="AX1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AY1" s="9"/>
+      <c r="AY1" s="15"/>
     </row>
     <row r="2" spans="1:51">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="15" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="W2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="X2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="Z2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AC2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AD2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AE2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AF2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AG2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AH2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AI2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AK2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AL2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AM2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AN2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AO2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AP2" s="13" t="s">
+      <c r="AP2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AR2" s="12" t="s">
+      <c r="AR2" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="AS2" s="12" t="s">
+      <c r="AS2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AT2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AU2" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AV2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AW2" s="9" t="s">
+      <c r="AW2" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AX2" s="9" t="s">
+      <c r="AX2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AY2" s="9" t="s">
+      <c r="AY2" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:51" ht="60">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
       <c r="M3" s="1" t="s">
         <v>49</v>
       </c>
@@ -1291,39 +1291,39 @@
       <c r="R3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="12"/>
-      <c r="AF3" s="12"/>
-      <c r="AG3" s="12"/>
-      <c r="AH3" s="12"/>
-      <c r="AI3" s="12"/>
-      <c r="AJ3" s="12"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="12"/>
-      <c r="AM3" s="12"/>
-      <c r="AN3" s="12"/>
-      <c r="AO3" s="12"/>
-      <c r="AP3" s="14"/>
-      <c r="AQ3" s="12"/>
-      <c r="AR3" s="12"/>
-      <c r="AS3" s="12"/>
-      <c r="AT3" s="12"/>
-      <c r="AU3" s="12"/>
-      <c r="AV3" s="12"/>
-      <c r="AW3" s="9"/>
-      <c r="AX3" s="9"/>
-      <c r="AY3" s="9"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="19"/>
+      <c r="AQ3" s="14"/>
+      <c r="AR3" s="14"/>
+      <c r="AS3" s="14"/>
+      <c r="AT3" s="14"/>
+      <c r="AU3" s="14"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="15"/>
+      <c r="AX3" s="15"/>
+      <c r="AY3" s="15"/>
     </row>
     <row r="4" spans="1:51">
       <c r="A4" s="3"/>
@@ -35618,39 +35618,6 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:AB1"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="AW2:AW3"/>
-    <mergeCell ref="AX2:AX3"/>
-    <mergeCell ref="AY2:AY3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="AS2:AS3"/>
-    <mergeCell ref="AT2:AT3"/>
-    <mergeCell ref="AU2:AU3"/>
-    <mergeCell ref="AV2:AV3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="AC1:AV1"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
@@ -35667,6 +35634,39 @@
     <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AG2:AG3"/>
     <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="AC1:AV1"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AX2:AX3"/>
+    <mergeCell ref="AY2:AY3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="AR2:AR3"/>
+    <mergeCell ref="AS2:AS3"/>
+    <mergeCell ref="AT2:AT3"/>
+    <mergeCell ref="AU2:AU3"/>
+    <mergeCell ref="AV2:AV3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:AB1"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AW2:AW3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA4:AA6 AX4:AX650" xr:uid="{D74D00A6-1C7D-4BB8-B411-21F94D182A8B}">
